--- a/hardware/BOM.xlsx
+++ b/hardware/BOM.xlsx
@@ -1,25 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jager\Dropbox\Public\Geiger\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Source\SvnDocuments\Projekty\Zigbee-geiger\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4A323ED-4DDE-4878-82E7-57FF86447A65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23160" windowHeight="13080"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM_Radiation_2020-06-04_15-29-" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="74">
   <si>
     <t>ID</t>
   </si>
@@ -239,40 +245,28 @@
     <t>Ali</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>**</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> По какой то причине на aliexpress отсутствуют индуктивности в исполнении SMD данного номинала</t>
-    </r>
-  </si>
-  <si>
-    <t>точнее они есть, но стоят не дешево.</t>
-  </si>
-  <si>
     <t>* В качестве держателей для счетчика Гейгера используются держатели для предохранителей 6мм (расстояние между контактами 8мм).</t>
+  </si>
+  <si>
+    <t>fuse clips</t>
+  </si>
+  <si>
+    <t>600V ?</t>
+  </si>
+  <si>
+    <t>** Z jakiegoś powodu na AliExpress nie ma cewek indukcyjnych w wersji SMD o tej wartości znamionowej, a właściwie to są, ale nie są tanie.</t>
+  </si>
+  <si>
+    <t>brak</t>
+  </si>
+  <si>
+    <t>trymer</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -787,57 +781,59 @@
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="43">
-    <cellStyle name="20% — акцент1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% — акцент2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% — акцент3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% — акцент4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% — акцент5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% — акцент6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% — акцент1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% — акцент2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% — акцент3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% — акцент4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% — акцент5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% — акцент6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% — акцент1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% — акцент2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% — акцент3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% — акцент4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% — акцент5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% — акцент6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Акцент1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Акцент2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Акцент3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Акцент4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Акцент5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Акцент6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Ввод " xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Вывод" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Вычисление" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Гиперссылка" xfId="42" builtinId="8"/>
-    <cellStyle name="Заголовок 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Заголовок 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Заголовок 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Заголовок 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Итог" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Контрольная ячейка" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Название" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Нейтральный" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Плохой" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Пояснение" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Примечание" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Связанная ячейка" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Текст предупреждения" xfId="14" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="Хороший" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Hyperlink" xfId="42" builtinId="8"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1114,16 +1110,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="22.44140625" customWidth="1"/>
-    <col min="3" max="3" width="12.5546875" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="2" max="2" width="22.42578125" customWidth="1"/>
+    <col min="3" max="3" width="20.5703125" customWidth="1"/>
+    <col min="4" max="4" width="44.42578125" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1140,7 +1137,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1163,7 +1160,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1180,7 +1177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1197,7 +1194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1214,7 +1211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1231,7 +1228,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1248,7 +1245,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1265,7 +1262,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1282,7 +1279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1299,7 +1296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1316,7 +1313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1333,7 +1330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1350,7 +1347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1366,8 +1363,11 @@
       <c r="E14">
         <v>2</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G14">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>15</v>
       </c>
@@ -1390,7 +1390,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>16</v>
       </c>
@@ -1410,7 +1410,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>17</v>
       </c>
@@ -1426,8 +1426,11 @@
       <c r="E17">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="I17" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>18</v>
       </c>
@@ -1444,7 +1447,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>19</v>
       </c>
@@ -1461,7 +1464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>20</v>
       </c>
@@ -1478,7 +1481,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>21</v>
       </c>
@@ -1494,8 +1497,11 @@
       <c r="E21">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G21" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>22</v>
       </c>
@@ -1511,8 +1517,17 @@
       <c r="E22">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="I22" t="s">
+        <v>72</v>
+      </c>
+      <c r="J22" s="4">
+        <v>3314</v>
+      </c>
+      <c r="K22" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>23</v>
       </c>
@@ -1529,7 +1544,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>24</v>
       </c>
@@ -1549,35 +1564,35 @@
         <v>62</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B27" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B28" t="s">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B27" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
         <v>69</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B3" r:id="rId1"/>
-    <hyperlink ref="B11" r:id="rId2"/>
-    <hyperlink ref="B16" r:id="rId3"/>
-    <hyperlink ref="F16" r:id="rId4"/>
-    <hyperlink ref="B24" r:id="rId5"/>
-    <hyperlink ref="F24" r:id="rId6"/>
-    <hyperlink ref="B15" r:id="rId7" display="10mH"/>
-    <hyperlink ref="F2" r:id="rId8"/>
-    <hyperlink ref="G2" r:id="rId9"/>
-    <hyperlink ref="F15" r:id="rId10"/>
-    <hyperlink ref="G15" r:id="rId11"/>
-    <hyperlink ref="B26" r:id="rId12"/>
+    <hyperlink ref="B3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="B11" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="B16" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="F16" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="B24" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="F24" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="B15" r:id="rId7" display="10mH" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="F2" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="G2" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="F15" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="G15" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="B26" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId13"/>
